--- a/backend/data/financials_by_company/0GO.F.xlsx
+++ b/backend/data/financials_by_company/0GO.F.xlsx
@@ -617,450 +617,450 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-5068.430474</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.082804</v>
+        <v>0.161872</v>
       </c>
       <c r="D2" t="n">
-        <v>-1159891</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-61210</v>
-      </c>
+        <v>-1843290</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>-1058622</v>
+        <v>-1544346</v>
       </c>
       <c r="H2" t="n">
-        <v>-1159891</v>
+        <v>-1843290</v>
       </c>
       <c r="I2" t="n">
-        <v>-1159891</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+        <v>-1843290</v>
+      </c>
+      <c r="J2" t="n">
+        <v>677</v>
+      </c>
+      <c r="K2" t="n">
+        <v>677</v>
+      </c>
       <c r="L2" t="n">
-        <v>-941270.4304740001</v>
+        <v>-1544346</v>
       </c>
       <c r="M2" t="n">
-        <v>-1058622</v>
+        <v>-1544346</v>
       </c>
       <c r="N2" t="n">
-        <v>1167173</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>1843290</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-1843290</v>
+      </c>
       <c r="P2" t="n">
-        <v>340881486</v>
+        <v>181080349</v>
       </c>
       <c r="Q2" t="n">
-        <v>340386906</v>
+        <v>181080349</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.0031</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0031</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>-1058622</v>
+        <v>-1544346</v>
       </c>
       <c r="U2" t="n">
-        <v>-1058622</v>
+        <v>-1544346</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-1058622</v>
-      </c>
-      <c r="X2" t="n">
-        <v>61367</v>
-      </c>
+        <v>-1544346</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
-        <v>-1119989</v>
+        <v>-1544346</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1119989</v>
+        <v>-1544346</v>
       </c>
       <c r="AA2" t="n">
-        <v>-101112</v>
+        <v>-298267</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1221101</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-61210</v>
-      </c>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+        <v>-1842613</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="n">
+        <v>677</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>677</v>
+      </c>
       <c r="AF2" t="n">
-        <v>-1159891</v>
+        <v>-1843290</v>
       </c>
       <c r="AG2" t="n">
-        <v>1167173</v>
+        <v>1843290</v>
       </c>
       <c r="AH2" t="n">
-        <v>390387</v>
+        <v>1179425</v>
       </c>
       <c r="AI2" t="n">
-        <v>551559</v>
+        <v>663865</v>
       </c>
       <c r="AJ2" t="n">
-        <v>551559</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>7282</v>
-      </c>
+        <v>663865</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
-        <v>7282</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>7282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.10376</v>
+        <v>0.137437</v>
       </c>
       <c r="D3" t="n">
-        <v>-1335419</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1193260</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="H3" t="n">
-        <v>-1335419</v>
+        <v>-1193260</v>
       </c>
       <c r="I3" t="n">
-        <v>-1335419</v>
+        <v>-1193260</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="M3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="N3" t="n">
-        <v>1337372</v>
+        <v>1193260</v>
       </c>
       <c r="O3" t="n">
-        <v>-1424594</v>
+        <v>-1193260</v>
       </c>
       <c r="P3" t="n">
-        <v>242889938</v>
+        <v>186422541</v>
       </c>
       <c r="Q3" t="n">
-        <v>242889938</v>
+        <v>186422541</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.0052</v>
+        <v>-0.0055</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0052</v>
+        <v>-0.0055</v>
       </c>
       <c r="T3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="U3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-1269331</v>
+        <v>-1029261</v>
       </c>
       <c r="X3" t="n">
-        <v>7447</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-1276778</v>
+        <v>-1029261</v>
       </c>
       <c r="Z3" t="n">
-        <v>-1276778</v>
+        <v>-1029261</v>
       </c>
       <c r="AA3" t="n">
-        <v>-147816</v>
+        <v>-163998</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1424594</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1193259</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1335419</v>
+        <v>-1193260</v>
       </c>
       <c r="AG3" t="n">
-        <v>1337372</v>
+        <v>1193260</v>
       </c>
       <c r="AH3" t="n">
-        <v>619392</v>
+        <v>577525</v>
       </c>
       <c r="AI3" t="n">
-        <v>486202</v>
+        <v>615735</v>
       </c>
       <c r="AJ3" t="n">
-        <v>486202</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1953</v>
-      </c>
+        <v>615735</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="n">
-        <v>1953</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1953</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.137437</v>
+        <v>0.10376</v>
       </c>
       <c r="D4" t="n">
-        <v>-1193260</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>-1335419</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="H4" t="n">
-        <v>-1193260</v>
+        <v>-1335419</v>
       </c>
       <c r="I4" t="n">
-        <v>-1193260</v>
+        <v>-1335419</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="M4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="N4" t="n">
-        <v>1193260</v>
+        <v>1337372</v>
       </c>
       <c r="O4" t="n">
-        <v>-1193260</v>
+        <v>-1424594</v>
       </c>
       <c r="P4" t="n">
-        <v>186422541</v>
+        <v>242889938</v>
       </c>
       <c r="Q4" t="n">
-        <v>186422541</v>
+        <v>242889938</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.0055</v>
+        <v>-0.0052</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0055</v>
+        <v>-0.0052</v>
       </c>
       <c r="T4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="U4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-1029261</v>
+        <v>-1269331</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>7447</v>
       </c>
       <c r="Y4" t="n">
-        <v>-1029261</v>
+        <v>-1276778</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1029261</v>
+        <v>-1276778</v>
       </c>
       <c r="AA4" t="n">
-        <v>-163998</v>
+        <v>-147816</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1193259</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>-1424594</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1193260</v>
+        <v>-1335419</v>
       </c>
       <c r="AG4" t="n">
-        <v>1193260</v>
+        <v>1337372</v>
       </c>
       <c r="AH4" t="n">
-        <v>577525</v>
+        <v>619392</v>
       </c>
       <c r="AI4" t="n">
-        <v>615735</v>
+        <v>486202</v>
       </c>
       <c r="AJ4" t="n">
-        <v>615735</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>486202</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1953</v>
+      </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1953</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-5068.430474</v>
       </c>
       <c r="C5" t="n">
-        <v>0.161872</v>
+        <v>0.082804</v>
       </c>
       <c r="D5" t="n">
-        <v>-1843290</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>-1159891</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-61210</v>
+      </c>
       <c r="G5" t="n">
-        <v>-1544346</v>
+        <v>-1058622</v>
       </c>
       <c r="H5" t="n">
-        <v>-1843290</v>
+        <v>-1159891</v>
       </c>
       <c r="I5" t="n">
-        <v>-1843290</v>
-      </c>
-      <c r="J5" t="n">
-        <v>677</v>
-      </c>
-      <c r="K5" t="n">
-        <v>677</v>
-      </c>
+        <v>-1159891</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-1544346</v>
+        <v>-941270.4304740001</v>
       </c>
       <c r="M5" t="n">
-        <v>-1544346</v>
+        <v>-1058622</v>
       </c>
       <c r="N5" t="n">
-        <v>1843290</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1843290</v>
-      </c>
+        <v>1167173</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>181080349</v>
+        <v>340881486</v>
       </c>
       <c r="Q5" t="n">
-        <v>181080349</v>
+        <v>340386906</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0031</v>
       </c>
       <c r="T5" t="n">
-        <v>-1544346</v>
+        <v>-1058622</v>
       </c>
       <c r="U5" t="n">
-        <v>-1544346</v>
+        <v>-1058622</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-1544346</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-1058622</v>
+      </c>
+      <c r="X5" t="n">
+        <v>61367</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-1544346</v>
+        <v>-1119989</v>
       </c>
       <c r="Z5" t="n">
-        <v>-1544346</v>
+        <v>-1119989</v>
       </c>
       <c r="AA5" t="n">
-        <v>-298267</v>
+        <v>-101112</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1842613</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="n">
-        <v>677</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>677</v>
-      </c>
+        <v>-1221101</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>-61210</v>
+      </c>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
-        <v>-1843290</v>
+        <v>-1159891</v>
       </c>
       <c r="AG5" t="n">
-        <v>1843290</v>
+        <v>1167173</v>
       </c>
       <c r="AH5" t="n">
-        <v>1179425</v>
+        <v>390387</v>
       </c>
       <c r="AI5" t="n">
-        <v>663865</v>
+        <v>551559</v>
       </c>
       <c r="AJ5" t="n">
-        <v>663865</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+        <v>551559</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>7282</v>
+      </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>7282</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>7282</v>
       </c>
     </row>
   </sheetData>
@@ -1246,408 +1246,408 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>394780349</v>
+        <v>181080349</v>
       </c>
       <c r="D2" t="n">
-        <v>394780349</v>
+        <v>181080349</v>
       </c>
       <c r="E2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="F2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="G2" t="n">
-        <v>651402</v>
+        <v>2129653</v>
       </c>
       <c r="H2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="I2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="J2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="K2" t="n">
-        <v>651402</v>
-      </c>
-      <c r="L2" t="n">
-        <v>3755</v>
-      </c>
+        <v>2129653</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>647647</v>
+        <v>2129653</v>
       </c>
       <c r="N2" t="n">
-        <v>8385600</v>
+        <v>8350780</v>
       </c>
       <c r="O2" t="n">
-        <v>-10399006</v>
+        <v>-7032153</v>
       </c>
       <c r="P2" t="n">
-        <v>14940829</v>
+        <v>13945602</v>
       </c>
       <c r="Q2" t="n">
-        <v>1579121</v>
+        <v>724321</v>
       </c>
       <c r="R2" t="n">
-        <v>1579121</v>
+        <v>724321</v>
       </c>
       <c r="S2" t="n">
-        <v>124367</v>
+        <v>212730</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>124367</v>
+        <v>212730</v>
       </c>
       <c r="V2" t="n">
-        <v>28796</v>
+        <v>184820</v>
       </c>
       <c r="W2" t="n">
-        <v>5472</v>
+        <v>4474</v>
       </c>
       <c r="X2" t="n">
-        <v>23324</v>
+        <v>180346</v>
       </c>
       <c r="Y2" t="n">
-        <v>775769</v>
+        <v>2342383</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>775769</v>
+        <v>2342383</v>
       </c>
       <c r="AD2" t="n">
-        <v>15130</v>
+        <v>7013</v>
       </c>
       <c r="AE2" t="n">
-        <v>7841</v>
+        <v>14642</v>
       </c>
       <c r="AF2" t="n">
-        <v>126826</v>
+        <v>536704</v>
       </c>
       <c r="AG2" t="n">
-        <v>625972</v>
+        <v>1784024</v>
       </c>
       <c r="AH2" t="n">
-        <v>625972</v>
+        <v>1784024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>268780349</v>
+        <v>233780349</v>
       </c>
       <c r="D3" t="n">
-        <v>268780349</v>
+        <v>233780349</v>
       </c>
       <c r="E3" t="n">
-        <v>1066426</v>
+        <v>2088158</v>
       </c>
       <c r="F3" t="n">
-        <v>1127636</v>
+        <v>2088158</v>
       </c>
       <c r="G3" t="n">
-        <v>1132431</v>
+        <v>2088158</v>
       </c>
       <c r="H3" t="n">
-        <v>1066426</v>
+        <v>2088158</v>
       </c>
       <c r="I3" t="n">
-        <v>1127636</v>
+        <v>2088158</v>
       </c>
       <c r="J3" t="n">
-        <v>1127636</v>
+        <v>2088158</v>
       </c>
       <c r="K3" t="n">
-        <v>1193641</v>
+        <v>2088158</v>
       </c>
       <c r="L3" t="n">
-        <v>66005</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1127636</v>
+        <v>2088158</v>
       </c>
       <c r="N3" t="n">
-        <v>8378210</v>
+        <v>8374779</v>
       </c>
       <c r="O3" t="n">
-        <v>-9341267</v>
+        <v>-8061414</v>
       </c>
       <c r="P3" t="n">
-        <v>14874469</v>
+        <v>14698569</v>
       </c>
       <c r="Q3" t="n">
-        <v>1075121</v>
+        <v>935121</v>
       </c>
       <c r="R3" t="n">
-        <v>1075121</v>
+        <v>935121</v>
       </c>
       <c r="S3" t="n">
-        <v>81726</v>
+        <v>77889</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>81726</v>
+        <v>77889</v>
       </c>
       <c r="V3" t="n">
-        <v>26224</v>
+        <v>40722</v>
       </c>
       <c r="W3" t="n">
-        <v>6022</v>
+        <v>4966</v>
       </c>
       <c r="X3" t="n">
-        <v>20202</v>
+        <v>35756</v>
       </c>
       <c r="Y3" t="n">
-        <v>1275367</v>
+        <v>2166047</v>
       </c>
       <c r="Z3" t="n">
-        <v>61210</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>61210</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>61210</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1214157</v>
+        <v>2166047</v>
       </c>
       <c r="AD3" t="n">
-        <v>10613</v>
+        <v>36888</v>
       </c>
       <c r="AE3" t="n">
-        <v>3644</v>
+        <v>27000</v>
       </c>
       <c r="AF3" t="n">
-        <v>172788</v>
+        <v>182630</v>
       </c>
       <c r="AG3" t="n">
-        <v>1027112</v>
+        <v>1919529</v>
       </c>
       <c r="AH3" t="n">
-        <v>1027112</v>
+        <v>1919529</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>233780349</v>
+        <v>268780349</v>
       </c>
       <c r="D4" t="n">
-        <v>233780349</v>
+        <v>268780349</v>
       </c>
       <c r="E4" t="n">
-        <v>2088158</v>
+        <v>1066426</v>
       </c>
       <c r="F4" t="n">
-        <v>2088158</v>
+        <v>1127636</v>
       </c>
       <c r="G4" t="n">
-        <v>2088158</v>
+        <v>1132431</v>
       </c>
       <c r="H4" t="n">
-        <v>2088158</v>
+        <v>1066426</v>
       </c>
       <c r="I4" t="n">
-        <v>2088158</v>
+        <v>1127636</v>
       </c>
       <c r="J4" t="n">
-        <v>2088158</v>
+        <v>1127636</v>
       </c>
       <c r="K4" t="n">
-        <v>2088158</v>
+        <v>1193641</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>66005</v>
       </c>
       <c r="M4" t="n">
-        <v>2088158</v>
+        <v>1127636</v>
       </c>
       <c r="N4" t="n">
-        <v>8374779</v>
+        <v>8378210</v>
       </c>
       <c r="O4" t="n">
-        <v>-8061414</v>
+        <v>-9341267</v>
       </c>
       <c r="P4" t="n">
-        <v>14698569</v>
+        <v>14874469</v>
       </c>
       <c r="Q4" t="n">
-        <v>935121</v>
+        <v>1075121</v>
       </c>
       <c r="R4" t="n">
-        <v>935121</v>
+        <v>1075121</v>
       </c>
       <c r="S4" t="n">
-        <v>77889</v>
+        <v>81726</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>77889</v>
+        <v>81726</v>
       </c>
       <c r="V4" t="n">
-        <v>40722</v>
+        <v>26224</v>
       </c>
       <c r="W4" t="n">
-        <v>4966</v>
+        <v>6022</v>
       </c>
       <c r="X4" t="n">
-        <v>35756</v>
+        <v>20202</v>
       </c>
       <c r="Y4" t="n">
-        <v>2166047</v>
+        <v>1275367</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>61210</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>61210</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>61210</v>
       </c>
       <c r="AC4" t="n">
-        <v>2166047</v>
+        <v>1214157</v>
       </c>
       <c r="AD4" t="n">
-        <v>36888</v>
+        <v>10613</v>
       </c>
       <c r="AE4" t="n">
-        <v>27000</v>
+        <v>3644</v>
       </c>
       <c r="AF4" t="n">
-        <v>182630</v>
+        <v>172788</v>
       </c>
       <c r="AG4" t="n">
-        <v>1919529</v>
+        <v>1027112</v>
       </c>
       <c r="AH4" t="n">
-        <v>1919529</v>
+        <v>1027112</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
-        <v>181080349</v>
+        <v>394780349</v>
       </c>
       <c r="D5" t="n">
-        <v>181080349</v>
+        <v>394780349</v>
       </c>
       <c r="E5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="F5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="G5" t="n">
-        <v>2129653</v>
+        <v>651402</v>
       </c>
       <c r="H5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="I5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="J5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="K5" t="n">
-        <v>2129653</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>651402</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3755</v>
+      </c>
       <c r="M5" t="n">
-        <v>2129653</v>
+        <v>647647</v>
       </c>
       <c r="N5" t="n">
-        <v>8350780</v>
+        <v>8385600</v>
       </c>
       <c r="O5" t="n">
-        <v>-7032153</v>
+        <v>-10399006</v>
       </c>
       <c r="P5" t="n">
-        <v>13945602</v>
+        <v>14940829</v>
       </c>
       <c r="Q5" t="n">
-        <v>724321</v>
+        <v>1579121</v>
       </c>
       <c r="R5" t="n">
-        <v>724321</v>
+        <v>1579121</v>
       </c>
       <c r="S5" t="n">
-        <v>212730</v>
+        <v>124367</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>212730</v>
+        <v>124367</v>
       </c>
       <c r="V5" t="n">
-        <v>184820</v>
+        <v>28796</v>
       </c>
       <c r="W5" t="n">
-        <v>4474</v>
+        <v>5472</v>
       </c>
       <c r="X5" t="n">
-        <v>180346</v>
+        <v>23324</v>
       </c>
       <c r="Y5" t="n">
-        <v>2342383</v>
+        <v>775769</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
       <c r="AC5" t="n">
-        <v>2342383</v>
+        <v>775769</v>
       </c>
       <c r="AD5" t="n">
-        <v>7013</v>
+        <v>15130</v>
       </c>
       <c r="AE5" t="n">
-        <v>14642</v>
+        <v>7841</v>
       </c>
       <c r="AF5" t="n">
-        <v>536704</v>
+        <v>126826</v>
       </c>
       <c r="AG5" t="n">
-        <v>1784024</v>
+        <v>625972</v>
       </c>
       <c r="AH5" t="n">
-        <v>1784024</v>
+        <v>625972</v>
       </c>
     </row>
   </sheetData>
@@ -1778,264 +1778,264 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-971500</v>
+        <v>-1772232</v>
       </c>
       <c r="C2" t="n">
-        <v>630000</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>625972</v>
+        <v>1784024</v>
       </c>
       <c r="E2" t="n">
-        <v>1027112</v>
+        <v>3555579</v>
       </c>
       <c r="F2" t="n">
-        <v>-401140</v>
+        <v>-1771555</v>
       </c>
       <c r="G2" t="n">
-        <v>570360</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>677</v>
+      </c>
+      <c r="H2" t="n">
+        <v>677</v>
+      </c>
       <c r="I2" t="n">
-        <v>630000</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>630000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-971500</v>
+        <v>-1772232</v>
       </c>
       <c r="P2" t="n">
-        <v>147816</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>33185</v>
+        <v>54393</v>
       </c>
       <c r="R2" t="n">
-        <v>42641</v>
+        <v>43648</v>
       </c>
       <c r="S2" t="n">
-        <v>-9456</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>10745</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-677</v>
+      </c>
       <c r="U2" t="n">
-        <v>7390</v>
+        <v>16665</v>
       </c>
       <c r="V2" t="n">
-        <v>-101112</v>
+        <v>-298267</v>
       </c>
       <c r="W2" t="n">
-        <v>-1119989</v>
+        <v>-1544346</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1209098</v>
+        <v>-828263</v>
       </c>
       <c r="C3" t="n">
-        <v>350000</v>
+        <v>1054000</v>
       </c>
       <c r="D3" t="n">
-        <v>1027112</v>
+        <v>1919529</v>
       </c>
       <c r="E3" t="n">
-        <v>1919529</v>
+        <v>1784024</v>
       </c>
       <c r="F3" t="n">
-        <v>-892417</v>
+        <v>135505</v>
       </c>
       <c r="G3" t="n">
-        <v>315900</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>963768</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
       <c r="I3" t="n">
-        <v>350000</v>
+        <v>1054000</v>
       </c>
       <c r="J3" t="n">
-        <v>350000</v>
+        <v>1054000</v>
       </c>
       <c r="K3" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>781</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-1209098</v>
+        <v>-828263</v>
       </c>
       <c r="P3" t="n">
-        <v>163997</v>
+        <v>513151</v>
       </c>
       <c r="Q3" t="n">
-        <v>48068</v>
+        <v>-172153</v>
       </c>
       <c r="R3" t="n">
-        <v>3838</v>
+        <v>-134841</v>
       </c>
       <c r="S3" t="n">
-        <v>44230</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>-37312</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-1</v>
+      </c>
       <c r="U3" t="n">
-        <v>3431</v>
+        <v>23999</v>
       </c>
       <c r="V3" t="n">
-        <v>-147816</v>
+        <v>-163998</v>
       </c>
       <c r="W3" t="n">
-        <v>-1276778</v>
+        <v>-1029261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-828263</v>
+        <v>-1209098</v>
       </c>
       <c r="C4" t="n">
-        <v>1054000</v>
+        <v>350000</v>
       </c>
       <c r="D4" t="n">
+        <v>1027112</v>
+      </c>
+      <c r="E4" t="n">
         <v>1919529</v>
       </c>
-      <c r="E4" t="n">
-        <v>1784024</v>
-      </c>
       <c r="F4" t="n">
-        <v>135505</v>
+        <v>-892417</v>
       </c>
       <c r="G4" t="n">
-        <v>963768</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
+        <v>315900</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>1054000</v>
+        <v>350000</v>
       </c>
       <c r="J4" t="n">
-        <v>1054000</v>
+        <v>350000</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>-828263</v>
+        <v>-1209098</v>
       </c>
       <c r="P4" t="n">
-        <v>513151</v>
+        <v>163997</v>
       </c>
       <c r="Q4" t="n">
-        <v>-172153</v>
+        <v>48068</v>
       </c>
       <c r="R4" t="n">
-        <v>-134841</v>
+        <v>3838</v>
       </c>
       <c r="S4" t="n">
-        <v>-37312</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
+        <v>44230</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>23999</v>
+        <v>3431</v>
       </c>
       <c r="V4" t="n">
-        <v>-163998</v>
+        <v>-147816</v>
       </c>
       <c r="W4" t="n">
-        <v>-1029261</v>
+        <v>-1276778</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1772232</v>
+        <v>-971500</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="D5" t="n">
-        <v>1784024</v>
+        <v>625972</v>
       </c>
       <c r="E5" t="n">
-        <v>3555579</v>
+        <v>1027112</v>
       </c>
       <c r="F5" t="n">
-        <v>-1771555</v>
+        <v>-401140</v>
       </c>
       <c r="G5" t="n">
-        <v>677</v>
-      </c>
-      <c r="H5" t="n">
-        <v>677</v>
-      </c>
+        <v>570360</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+        <v>630000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
       <c r="O5" t="n">
-        <v>-1772232</v>
+        <v>-971500</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>147816</v>
       </c>
       <c r="Q5" t="n">
-        <v>54393</v>
+        <v>33185</v>
       </c>
       <c r="R5" t="n">
-        <v>43648</v>
+        <v>42641</v>
       </c>
       <c r="S5" t="n">
-        <v>10745</v>
-      </c>
-      <c r="T5" t="n">
-        <v>-677</v>
-      </c>
+        <v>-9456</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>16665</v>
+        <v>7390</v>
       </c>
       <c r="V5" t="n">
-        <v>-298267</v>
+        <v>-101112</v>
       </c>
       <c r="W5" t="n">
-        <v>-1544346</v>
+        <v>-1119989</v>
       </c>
     </row>
   </sheetData>
@@ -2525,197 +2525,197 @@
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CT1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="ED1" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Luke Sebastian Cairns', 'age': 47, 'title': 'Executive Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 50807, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. David Horn Solomon M.D.', 'age': 65, 'title': 'CEO &amp; Director', 'yearBorn': 1960, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Rob  Harris', 'title': 'Head of CMC Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Fiona  McLaughlin FSB, Ph.D.', 'age': 55, 'title': 'Head of Research &amp; Development', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Edbrooke Ph.D.', 'title': 'Head of Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Margaret  Courtney Ph.D.', 'title': 'Head of Chemistry, Manufacturing &amp; Controls', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Andrew  Leishman', 'title': 'Consultant', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Luke Sebastian Cairns', 'age': 47, 'title': 'Executive Director', 'yearBorn': 1978, 'fiscalYear': 2024, 'totalPay': 50696, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. David Horn Solomon M.D.', 'age': 65, 'title': 'CEO &amp; Director', 'yearBorn': 1960, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Rob  Harris', 'title': 'Head of CMC Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Fiona  McLaughlin FSB, Ph.D.', 'age': 55, 'title': 'Head of Research &amp; Development', 'yearBorn': 1970, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mark  Edbrooke Ph.D.', 'title': 'Head of Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Margaret  Courtney Ph.D.', 'title': 'Head of Chemistry, Manufacturing &amp; Controls', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Andrew  Leishman', 'title': 'Consultant', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -2821,64 +2821,64 @@
         <v>0.0005</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="Y2" t="n">
         <v>0.0005</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.712</v>
       </c>
       <c r="AE2" t="n">
-        <v>2375</v>
+        <v>21775</v>
       </c>
       <c r="AF2" t="n">
-        <v>2375</v>
+        <v>21775</v>
       </c>
       <c r="AG2" t="n">
-        <v>38</v>
+        <v>351</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2177</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2177</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.027</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="AL2" t="n">
-        <v>416140</v>
+        <v>4161401</v>
       </c>
       <c r="AM2" t="n">
-        <v>6246788</v>
+        <v>5513687</v>
       </c>
       <c r="AN2" t="n">
         <v>0.0005</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.026</v>
+        <v>0.0265</v>
       </c>
       <c r="AP2" t="n">
         <v>0.14</v>
@@ -2887,13 +2887,13 @@
         <v>0.0005</v>
       </c>
       <c r="AR2" t="n">
-        <v>58.89329</v>
+        <v>588.93304</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.0005</v>
+        <v>0.00102</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.0009974999999999999</v>
+        <v>0.0010925</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>-1438558</v>
+        <v>1155917</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
@@ -2931,10 +2931,10 @@
         <v>832280349</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0034641398</v>
+        <v>0.0034597681</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.14433599</v>
+        <v>1.4451835</v>
       </c>
       <c r="BH2" t="n">
         <v>1735603200</v>
@@ -2952,13 +2952,13 @@
         <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-203.589</v>
+        <v>163.589</v>
       </c>
       <c r="BN2" t="n">
         <v>-0.5</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0005</v>
+        <v>0.005</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3061,148 +3061,148 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>finmb_283400218</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="CW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>0.00398</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>3.9019608</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.0039075</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>3.5766587</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>N4 Pharma Plc</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="CR2" t="n">
-        <v>1780380473</v>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CT2" t="inlineStr">
-        <is>
-          <t>finmb_283400218</t>
-        </is>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CV2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="CW2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DH2" t="n">
+        <v>1782112090</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Thalia Therapeutics PLC       R</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>Thalia Therapeutics Plc</t>
         </is>
       </c>
-      <c r="DB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="DD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
+      <c r="DL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
         <v>1611558000000</v>
       </c>
-      <c r="DF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>5.0E-4 - 5.0E-4</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DN2" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>0.005 - 0.005</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>38</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>5.0E-4 - 0.026</t>
-        </is>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.025500001</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.9807693</v>
-      </c>
-      <c r="DO2" t="n">
+      <c r="DQ2" t="n">
+        <v>351</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>8.999999000000001</v>
+      </c>
+      <c r="DT2" t="inlineStr">
+        <is>
+          <t>5.0E-4 - 0.0265</t>
+        </is>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.021499999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.8113207</v>
+      </c>
+      <c r="DW2" t="n">
         <v>-50</v>
       </c>
-      <c r="DP2" t="n">
+      <c r="DX2" t="n">
         <v>1758526200</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DY2" t="n">
         <v>1758871800</v>
       </c>
-      <c r="DR2" t="b">
+      <c r="DZ2" t="b">
         <v>1</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EA2" t="n">
         <v>-0</v>
       </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.0004975</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.49874687</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>N4 Pharma Plc</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="EC2" t="b">
-        <v>0</v>
+      <c r="EB2" t="n">
+        <v>899.9999</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.005</v>
       </c>
       <c r="ED2" t="inlineStr"/>
     </row>
